--- a/CPT Dataset Alpha - workflows of existing systems details/Workflows of existing systems details.xlsx
+++ b/CPT Dataset Alpha - workflows of existing systems details/Workflows of existing systems details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\CPT project\CPT dataset paper\repository-CPT-dataset-alpha-ICST-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\CPT project\CPT dataset paper\repository-CPT-dataset-alpha-ICST-2026\CPT Dataset Alpha - workflows of existing systems details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0C1318-09F9-4799-9BCA-99CEAB3B496C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E2C1BA-F351-4C34-8F4A-EC80766B43D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6150" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{8565883A-39B4-4ABD-93BD-118662CB21B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8565883A-39B4-4ABD-93BD-118662CB21B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="253">
   <si>
     <t>id</t>
   </si>
@@ -792,6 +792,9 @@
   </si>
   <si>
     <t>Critical system 5</t>
+  </si>
+  <si>
+    <t>CPT Dataset α – workflows of existing systems details</t>
   </si>
 </sst>
 </file>
@@ -808,14 +811,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -825,51 +820,58 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <name val="CMU Sans Serif"/>
       <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="Roboto"/>
+      <name val="CMU Sans Serif"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="Roboto"/>
+      <name val="CMU Sans Serif"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="CMU Sans Serif"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="CMU Sans Serif"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="CMU Sans Serif"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="CMU Sans Serif"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="CMU Sans Serif"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="CMU Sans Serif"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -969,60 +971,58 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1042,12 +1042,10 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
+        <name val="CMU Sans Serif"/>
         <charset val="238"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1055,20 +1053,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1083,7 +1067,8 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="0"/>
-        <name val="Roboto"/>
+        <name val="CMU Sans Serif"/>
+        <charset val="238"/>
         <scheme val="none"/>
       </font>
       <fill>
@@ -1107,34 +1092,7 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
+        <name val="CMU Sans Serif"/>
         <charset val="238"/>
         <scheme val="none"/>
       </font>
@@ -1173,8 +1131,7 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
+        <name val="CMU Sans Serif"/>
         <charset val="238"/>
         <scheme val="none"/>
       </font>
@@ -1207,6 +1164,9 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <color auto="1"/>
+        <name val="CMU Sans Serif"/>
+        <charset val="238"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -1228,9 +1188,50 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color auto="1"/>
-        <name val="Roboto"/>
+        <name val="CMU Sans Serif"/>
+        <charset val="238"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="CMU Sans Serif"/>
+        <charset val="238"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1262,13 +1263,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF284E3F"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF284E3F"/>
         </left>
@@ -1278,6 +1272,13 @@
         <top style="medium">
           <color rgb="FF284E3F"/>
         </top>
+        <bottom style="medium">
+          <color rgb="FF284E3F"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FF284E3F"/>
         </bottom>
@@ -1297,19 +1298,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3392FF2F-16F9-41B8-BF8C-5B4743914C38}" name="Table1" displayName="Table1" ref="A1:E87" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:E87" xr:uid="{3392FF2F-16F9-41B8-BF8C-5B4743914C38}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E87">
-    <sortCondition ref="A1:A87"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3392FF2F-16F9-41B8-BF8C-5B4743914C38}" name="Table1" displayName="Table1" ref="A2:E88" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="A2:E88" xr:uid="{3392FF2F-16F9-41B8-BF8C-5B4743914C38}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E88">
+    <sortCondition ref="A2:A88"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{0AEC7857-487D-447B-A8B9-A7E45F0C8653}" name="id" dataDxfId="0">
-      <calculatedColumnFormula>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{CC017974-1090-4EF7-843F-3D760995B85F}" name="Instance name" dataDxfId="6"/>
-    <tableColumn id="1" xr3:uid="{D383F827-8AF9-4F98-A4AD-F0838AA79A7B}" name="Algorithm design" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{CBA78A7F-B251-4782-9FEA-A8B2345A6CD7}" name="System" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{8F6B7612-462E-41C9-9967-7FA7F1697C09}" name="DOI / url" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{0AEC7857-487D-447B-A8B9-A7E45F0C8653}" name="id" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{CC017974-1090-4EF7-843F-3D760995B85F}" name="Instance name" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{D383F827-8AF9-4F98-A4AD-F0838AA79A7B}" name="Algorithm design" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{CBA78A7F-B251-4782-9FEA-A8B2345A6CD7}" name="System" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{8F6B7612-462E-41C9-9967-7FA7F1697C09}" name="DOI / url" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1635,1648 +1634,1575 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E88"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="81" customWidth="1"/>
-    <col min="5" max="5" width="58.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="81" style="1" customWidth="1"/>
+    <col min="5" max="5" width="58.21875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:5" ht="64.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:5" s="5" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B2" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="3" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="4" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="5" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="6" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="7" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="8" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="9" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E9" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="10" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E10" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="11" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E11" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="12" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="13" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E13" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="14" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="15" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E15" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="16" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C16" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="17" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="11">
         <v>15</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B17" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D17" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E17" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="18" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E18" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="19" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E19" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="20" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="21" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E21" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="22" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E22" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="23" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E23" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="24" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E24" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="25" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="26" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B26" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E26" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="27" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E27" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="28" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E28" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="29" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E29" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="30" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D30" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E30" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="31" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B31" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D31" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E31" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="32" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E32" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="33" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D33" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E33" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="34" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E34" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="35" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D35" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="36" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B36" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D36" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E36" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="37" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E37" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="38" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E38" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="39" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E39" s="7" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="40" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C40" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E40" s="7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="41" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B41" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D41" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E41" s="14" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="42" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C42" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E42" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="43" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E43" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="44" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E44" s="7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="45" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E45" s="7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="46" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="6">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E46" s="7" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="47" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B47" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C47" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E47" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="48" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E48" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="49" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C49" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D49" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E49" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="50" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="6">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B50" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C50" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D50" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E50" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="51" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B51" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C51" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E51" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="52" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="6">
         <v>50</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B52" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C52" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D52" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E52" s="15" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="53" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B53" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C53" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E53" s="6" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="54" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B54" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C54" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D54" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E54" s="6" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="55" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B55" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C55" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D55" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E55" s="6" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="56" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="6">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B56" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C56" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D56" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E56" s="7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="57" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C57" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D57" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E57" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="58" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="6">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B58" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C58" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D58" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E58" s="7" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="59" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E59" s="7" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="60" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B60" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C60" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D60" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E60" s="7" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="61" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B61" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C61" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D61" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E61" s="7" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="62" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B62" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C62" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D62" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E62" s="7" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="63" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B63" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C63" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D63" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E63" s="7" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="64" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C64" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D64" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E64" s="7" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="65" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C65" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D65" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E65" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="66" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B66" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D66" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E66" s="7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="67" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B67" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C67" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D67" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E67" s="7" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="68" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B68" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C68" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D68" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E68" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="69" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B69" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C69" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D69" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E69" s="7" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="70" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B70" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C70" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D70" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E70" s="7" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="71" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="6">
         <v>69</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B71" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C71" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D71" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E71" s="7" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="72" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="6">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B72" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C72" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D72" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="E72" s="7" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="73" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="6">
         <v>71</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B73" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C73" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D73" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E73" s="7" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="74" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B74" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C73" s="18"/>
-      <c r="D73" s="1" t="s">
+      <c r="C74" s="16"/>
+      <c r="D74" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E74" s="7" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="75" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="6">
         <v>101</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B75" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C75" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D75" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E75" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="76" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="6">
         <v>102</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B76" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D76" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E76" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="77" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="6">
         <v>103</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B77" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C77" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D77" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E77" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="78" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="6">
         <v>104</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B78" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C78" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D78" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E78" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="79" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="6">
         <v>105</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B79" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D79" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E79" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="80" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="6">
         <v>106</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B80" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D80" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E80" s="7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="81" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="6">
         <v>107</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B81" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D81" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E80" s="8" t="s">
+      <c r="E81" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="82" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="6">
         <v>108</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B82" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D82" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E82" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="83" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="6">
         <v>109</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B83" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D83" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E83" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="84" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="6">
         <v>110</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B84" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D84" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E84" s="7" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="85" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="6">
         <v>111</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B85" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D85" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E85" s="7" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="86" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="6">
         <v>112</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B86" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C86" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D86" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="E86" s="7" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="8">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="87" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="6">
         <v>201</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B87" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D87" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E87" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="15">
-        <f>_xlfn.NUMBERVALUE(LEFT(Table1[[#This Row],[Instance name]],FIND("_",Table1[[#This Row],[Instance name]])-1))</f>
+    <row r="88" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="17">
         <v>202</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B88" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C87" s="17" t="s">
+      <c r="C88" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D88" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="E87" s="8" t="s">
+      <c r="E88" s="6" t="s">
         <v>245</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E25" r:id="rId1" xr:uid="{CF1CA7E4-1336-471E-AC81-9E6EAF8A3FC2}"/>
-    <hyperlink ref="E51" r:id="rId2" xr:uid="{637B2B35-D918-451E-91A3-55DB05A7C8F9}"/>
-    <hyperlink ref="E60" r:id="rId3" xr:uid="{9A3CE231-B533-46E2-ABF7-285345A3EA80}"/>
-    <hyperlink ref="E38" r:id="rId4" xr:uid="{6E11B99C-E4BC-4D40-A978-B89148CECB49}"/>
-    <hyperlink ref="E61" r:id="rId5" xr:uid="{2BB1BEF7-2F60-4E13-A7D1-21875E698234}"/>
-    <hyperlink ref="E69" r:id="rId6" xr:uid="{B0277E21-ACFC-4D5F-A4AC-8A1786F644F5}"/>
-    <hyperlink ref="E6" r:id="rId7" xr:uid="{96BF8E31-C2ED-4750-A805-125A694CFF62}"/>
-    <hyperlink ref="E9" r:id="rId8" xr:uid="{DE089EC9-3830-4CC9-AC0B-37AAA654D3D8}"/>
-    <hyperlink ref="E14" r:id="rId9" xr:uid="{7CB247A8-5BCC-43AD-A30A-E9C00D688E94}"/>
-    <hyperlink ref="E15" r:id="rId10" xr:uid="{0D3631C0-1CDD-4085-ADC5-57306764F08F}"/>
-    <hyperlink ref="E17" r:id="rId11" xr:uid="{C94744CB-51E9-44BF-9DB3-1885B717CCD5}"/>
-    <hyperlink ref="E45" r:id="rId12" xr:uid="{0BACD8A8-4E0B-4D4E-853D-2846AB5E8008}"/>
-    <hyperlink ref="E65" r:id="rId13" xr:uid="{EDA78AA9-53D2-4720-AA1F-8F5614859FF1}"/>
-    <hyperlink ref="E67" r:id="rId14" xr:uid="{23E1DD49-1B23-4A58-B903-3D995D8C968E}"/>
-    <hyperlink ref="E71" r:id="rId15" xr:uid="{A44421AB-B381-4FB5-AC6F-F14975CF076C}"/>
-    <hyperlink ref="E46" r:id="rId16" xr:uid="{3348852A-A700-40E0-BAD3-10C0DC1BE7B7}"/>
-    <hyperlink ref="E47" r:id="rId17" xr:uid="{60964EE4-5237-4A61-AEE0-C2D8273E7FD3}"/>
-    <hyperlink ref="E48" r:id="rId18" xr:uid="{8880229E-DFD3-4E56-90C2-3DB3395B1732}"/>
-    <hyperlink ref="E11" r:id="rId19" xr:uid="{30E2DB0B-2D06-456D-B557-6E10796A19FF}"/>
-    <hyperlink ref="E35" r:id="rId20" xr:uid="{73EB2080-09D9-4314-8DAA-2274A1712539}"/>
-    <hyperlink ref="E36" r:id="rId21" xr:uid="{83B22DC7-0C55-44EA-9DC9-7146D79BD0DA}"/>
-    <hyperlink ref="E58" r:id="rId22" xr:uid="{A21D5017-7DB6-4171-87B0-FD08277587D5}"/>
-    <hyperlink ref="E12" r:id="rId23" xr:uid="{009465BA-D992-42BC-8B42-DA551CAB2253}"/>
-    <hyperlink ref="E76" r:id="rId24" xr:uid="{FCA02523-34BB-4A02-B750-43571DF9BD69}"/>
-    <hyperlink ref="E32" r:id="rId25" xr:uid="{BE428E2D-DE66-410F-8B04-4DF14B9EAF6D}"/>
-    <hyperlink ref="E57" r:id="rId26" xr:uid="{E2D9233C-50B8-49A1-8961-8B3BDA526BE2}"/>
-    <hyperlink ref="E84" r:id="rId27" xr:uid="{B3D8EE11-B9F4-4508-A779-0803465AD5F9}"/>
-    <hyperlink ref="E79" r:id="rId28" xr:uid="{19BB23B3-9343-4C8B-AABC-FBAB9ED3498D}"/>
-    <hyperlink ref="E39" r:id="rId29" xr:uid="{BF7D7E5F-DC73-4D1F-AFBF-49006C3FEF08}"/>
-    <hyperlink ref="E83" r:id="rId30" xr:uid="{E76CE23E-01D9-4774-A4A9-0DE87042F282}"/>
-    <hyperlink ref="E30" r:id="rId31" xr:uid="{2FB051A6-DC8B-45FE-B6CF-E30AB316C0FA}"/>
-    <hyperlink ref="E10" r:id="rId32" xr:uid="{8B4DC4D6-AC5B-45D4-A7A3-E8607680F8EF}"/>
-    <hyperlink ref="E13" r:id="rId33" xr:uid="{B9C215AE-E2B8-49A4-A165-9472C58B010A}"/>
-    <hyperlink ref="E31" r:id="rId34" xr:uid="{9F1E156E-C129-4411-BFD6-ADD0C5465AD4}"/>
-    <hyperlink ref="E78" r:id="rId35" xr:uid="{66350DD9-EC04-4564-82D8-84BAFBAA4C08}"/>
-    <hyperlink ref="E33" r:id="rId36" xr:uid="{E96D8E50-0F55-4F2F-B8F6-33761D049B26}"/>
-    <hyperlink ref="E34" r:id="rId37" xr:uid="{D84B056A-BFF0-4637-AC0C-C76F1E1B5EFA}"/>
-    <hyperlink ref="E43" r:id="rId38" xr:uid="{7EA2E294-E3B6-477B-870F-888CF6B3BA21}"/>
-    <hyperlink ref="E44" r:id="rId39" xr:uid="{8BC3CC51-D4F5-4BFA-8C69-933CFAA27751}"/>
-    <hyperlink ref="E16" r:id="rId40" xr:uid="{BF822055-D039-49A2-916C-BFB81753431D}"/>
-    <hyperlink ref="E24" r:id="rId41" xr:uid="{D955E6F2-7203-493E-957E-ECFAB28355B7}"/>
-    <hyperlink ref="E26" r:id="rId42" xr:uid="{AEBE843D-FDE5-4102-89E4-4818115334C9}"/>
-    <hyperlink ref="E27" r:id="rId43" xr:uid="{52B9139A-4A7B-4996-BC31-389CC01CC6FA}"/>
-    <hyperlink ref="E72" r:id="rId44" xr:uid="{D2991EAA-538F-4B15-B5BC-D17FDF77F11D}"/>
-    <hyperlink ref="E73" r:id="rId45" xr:uid="{3179E85D-03C2-4F5C-A665-2397A7BC9C4D}"/>
-    <hyperlink ref="E7" r:id="rId46" display="https://portal.so.ucr.ac.cr/sites/default/files/documents/2017_Analysis of Loan Application Process Using Process Mining.pdf" xr:uid="{38067E1A-28B6-49F8-A77A-F47984C48785}"/>
-    <hyperlink ref="E49" r:id="rId47" xr:uid="{566314B6-7B05-4F27-9CCF-751EA18EECF9}"/>
-    <hyperlink ref="E59" r:id="rId48" xr:uid="{4CBBBC22-ADF0-4FA6-A8F2-A0D5C2047BE6}"/>
-    <hyperlink ref="E63" r:id="rId49" xr:uid="{A2802774-40A5-4F10-B5AC-590754890D38}"/>
-    <hyperlink ref="E68" r:id="rId50" xr:uid="{C693B1A3-BC25-4D7E-8A69-C2EFA58858E4}"/>
-    <hyperlink ref="E8" r:id="rId51" xr:uid="{76A2C30C-821E-48F8-B8AC-34836A33FECC}"/>
-    <hyperlink ref="E2" r:id="rId52" xr:uid="{0C40B920-85AA-4EBD-942C-6D362E066F93}"/>
-    <hyperlink ref="E4" r:id="rId53" xr:uid="{FB43C47B-080B-425D-AE49-7CB66FFCA877}"/>
-    <hyperlink ref="E19" r:id="rId54" xr:uid="{ADA410F7-2033-42E9-893C-C73BEC52BBB3}"/>
-    <hyperlink ref="E85" r:id="rId55" xr:uid="{C68CE6CF-B1D8-4496-8ACA-B22291EF52D0}"/>
-    <hyperlink ref="E18" r:id="rId56" xr:uid="{689C7FE7-936A-4F5D-8BE8-0E06ACB96066}"/>
-    <hyperlink ref="E3" r:id="rId57" xr:uid="{56931A3E-09F5-4F5F-94F1-E75BB9C6DFC6}"/>
-    <hyperlink ref="E56" r:id="rId58" xr:uid="{2E6A6A58-722B-4B19-B4B8-9398626D7004}"/>
-    <hyperlink ref="E66" r:id="rId59" display="https://doi.org/10.1088/1742-6596/1986/1/012102?urlappend=%3Futm_source%3Dresearchgate.net%26medium%3Darticle" xr:uid="{E41E8DBF-54EA-4416-A23A-A0A78B3D3697}"/>
-    <hyperlink ref="E29" r:id="rId60" xr:uid="{1E5241C9-DBD6-4C59-AFAC-6620AE75E3AE}"/>
-    <hyperlink ref="E28" r:id="rId61" xr:uid="{297F2160-7FDA-4E61-8889-0B71276CD383}"/>
-    <hyperlink ref="E50" r:id="rId62" xr:uid="{72EECF10-CECD-464C-BB04-C3AB1A2473B5}"/>
-    <hyperlink ref="E70" r:id="rId63" xr:uid="{DCECEEEA-CC5C-4A5C-997B-17BED3201EE9}"/>
-    <hyperlink ref="E5" r:id="rId64" xr:uid="{00A5E618-BEB1-45F3-A05E-F2CC3A86EBE1}"/>
-    <hyperlink ref="E74" r:id="rId65" xr:uid="{FE8EA63D-DF79-4D3A-A081-43562A92D5E5}"/>
-    <hyperlink ref="E55" r:id="rId66" xr:uid="{E6C3BB6B-F8FC-42D8-8A3B-069A6360CF02}"/>
-    <hyperlink ref="E77" r:id="rId67" xr:uid="{6182ED48-FC33-4E17-89BD-BF1C73B01713}"/>
+    <hyperlink ref="E26" r:id="rId1" xr:uid="{CF1CA7E4-1336-471E-AC81-9E6EAF8A3FC2}"/>
+    <hyperlink ref="E52" r:id="rId2" xr:uid="{637B2B35-D918-451E-91A3-55DB05A7C8F9}"/>
+    <hyperlink ref="E61" r:id="rId3" xr:uid="{9A3CE231-B533-46E2-ABF7-285345A3EA80}"/>
+    <hyperlink ref="E39" r:id="rId4" xr:uid="{6E11B99C-E4BC-4D40-A978-B89148CECB49}"/>
+    <hyperlink ref="E62" r:id="rId5" xr:uid="{2BB1BEF7-2F60-4E13-A7D1-21875E698234}"/>
+    <hyperlink ref="E70" r:id="rId6" xr:uid="{B0277E21-ACFC-4D5F-A4AC-8A1786F644F5}"/>
+    <hyperlink ref="E7" r:id="rId7" xr:uid="{96BF8E31-C2ED-4750-A805-125A694CFF62}"/>
+    <hyperlink ref="E10" r:id="rId8" xr:uid="{DE089EC9-3830-4CC9-AC0B-37AAA654D3D8}"/>
+    <hyperlink ref="E15" r:id="rId9" xr:uid="{7CB247A8-5BCC-43AD-A30A-E9C00D688E94}"/>
+    <hyperlink ref="E16" r:id="rId10" xr:uid="{0D3631C0-1CDD-4085-ADC5-57306764F08F}"/>
+    <hyperlink ref="E18" r:id="rId11" xr:uid="{C94744CB-51E9-44BF-9DB3-1885B717CCD5}"/>
+    <hyperlink ref="E46" r:id="rId12" xr:uid="{0BACD8A8-4E0B-4D4E-853D-2846AB5E8008}"/>
+    <hyperlink ref="E66" r:id="rId13" xr:uid="{EDA78AA9-53D2-4720-AA1F-8F5614859FF1}"/>
+    <hyperlink ref="E68" r:id="rId14" xr:uid="{23E1DD49-1B23-4A58-B903-3D995D8C968E}"/>
+    <hyperlink ref="E72" r:id="rId15" xr:uid="{A44421AB-B381-4FB5-AC6F-F14975CF076C}"/>
+    <hyperlink ref="E47" r:id="rId16" xr:uid="{3348852A-A700-40E0-BAD3-10C0DC1BE7B7}"/>
+    <hyperlink ref="E48" r:id="rId17" xr:uid="{60964EE4-5237-4A61-AEE0-C2D8273E7FD3}"/>
+    <hyperlink ref="E49" r:id="rId18" xr:uid="{8880229E-DFD3-4E56-90C2-3DB3395B1732}"/>
+    <hyperlink ref="E12" r:id="rId19" xr:uid="{30E2DB0B-2D06-456D-B557-6E10796A19FF}"/>
+    <hyperlink ref="E36" r:id="rId20" xr:uid="{73EB2080-09D9-4314-8DAA-2274A1712539}"/>
+    <hyperlink ref="E37" r:id="rId21" xr:uid="{83B22DC7-0C55-44EA-9DC9-7146D79BD0DA}"/>
+    <hyperlink ref="E59" r:id="rId22" xr:uid="{A21D5017-7DB6-4171-87B0-FD08277587D5}"/>
+    <hyperlink ref="E13" r:id="rId23" xr:uid="{009465BA-D992-42BC-8B42-DA551CAB2253}"/>
+    <hyperlink ref="E77" r:id="rId24" xr:uid="{FCA02523-34BB-4A02-B750-43571DF9BD69}"/>
+    <hyperlink ref="E33" r:id="rId25" xr:uid="{BE428E2D-DE66-410F-8B04-4DF14B9EAF6D}"/>
+    <hyperlink ref="E58" r:id="rId26" xr:uid="{E2D9233C-50B8-49A1-8961-8B3BDA526BE2}"/>
+    <hyperlink ref="E85" r:id="rId27" xr:uid="{B3D8EE11-B9F4-4508-A779-0803465AD5F9}"/>
+    <hyperlink ref="E80" r:id="rId28" xr:uid="{19BB23B3-9343-4C8B-AABC-FBAB9ED3498D}"/>
+    <hyperlink ref="E40" r:id="rId29" xr:uid="{BF7D7E5F-DC73-4D1F-AFBF-49006C3FEF08}"/>
+    <hyperlink ref="E84" r:id="rId30" xr:uid="{E76CE23E-01D9-4774-A4A9-0DE87042F282}"/>
+    <hyperlink ref="E31" r:id="rId31" xr:uid="{2FB051A6-DC8B-45FE-B6CF-E30AB316C0FA}"/>
+    <hyperlink ref="E11" r:id="rId32" xr:uid="{8B4DC4D6-AC5B-45D4-A7A3-E8607680F8EF}"/>
+    <hyperlink ref="E14" r:id="rId33" xr:uid="{B9C215AE-E2B8-49A4-A165-9472C58B010A}"/>
+    <hyperlink ref="E32" r:id="rId34" xr:uid="{9F1E156E-C129-4411-BFD6-ADD0C5465AD4}"/>
+    <hyperlink ref="E79" r:id="rId35" xr:uid="{66350DD9-EC04-4564-82D8-84BAFBAA4C08}"/>
+    <hyperlink ref="E34" r:id="rId36" xr:uid="{E96D8E50-0F55-4F2F-B8F6-33761D049B26}"/>
+    <hyperlink ref="E35" r:id="rId37" xr:uid="{D84B056A-BFF0-4637-AC0C-C76F1E1B5EFA}"/>
+    <hyperlink ref="E44" r:id="rId38" xr:uid="{7EA2E294-E3B6-477B-870F-888CF6B3BA21}"/>
+    <hyperlink ref="E45" r:id="rId39" xr:uid="{8BC3CC51-D4F5-4BFA-8C69-933CFAA27751}"/>
+    <hyperlink ref="E17" r:id="rId40" xr:uid="{BF822055-D039-49A2-916C-BFB81753431D}"/>
+    <hyperlink ref="E25" r:id="rId41" xr:uid="{D955E6F2-7203-493E-957E-ECFAB28355B7}"/>
+    <hyperlink ref="E27" r:id="rId42" xr:uid="{AEBE843D-FDE5-4102-89E4-4818115334C9}"/>
+    <hyperlink ref="E28" r:id="rId43" xr:uid="{52B9139A-4A7B-4996-BC31-389CC01CC6FA}"/>
+    <hyperlink ref="E73" r:id="rId44" xr:uid="{D2991EAA-538F-4B15-B5BC-D17FDF77F11D}"/>
+    <hyperlink ref="E74" r:id="rId45" xr:uid="{3179E85D-03C2-4F5C-A665-2397A7BC9C4D}"/>
+    <hyperlink ref="E8" r:id="rId46" display="https://portal.so.ucr.ac.cr/sites/default/files/documents/2017_Analysis of Loan Application Process Using Process Mining.pdf" xr:uid="{38067E1A-28B6-49F8-A77A-F47984C48785}"/>
+    <hyperlink ref="E50" r:id="rId47" xr:uid="{566314B6-7B05-4F27-9CCF-751EA18EECF9}"/>
+    <hyperlink ref="E60" r:id="rId48" xr:uid="{4CBBBC22-ADF0-4FA6-A8F2-A0D5C2047BE6}"/>
+    <hyperlink ref="E64" r:id="rId49" xr:uid="{A2802774-40A5-4F10-B5AC-590754890D38}"/>
+    <hyperlink ref="E69" r:id="rId50" xr:uid="{C693B1A3-BC25-4D7E-8A69-C2EFA58858E4}"/>
+    <hyperlink ref="E9" r:id="rId51" xr:uid="{76A2C30C-821E-48F8-B8AC-34836A33FECC}"/>
+    <hyperlink ref="E3" r:id="rId52" xr:uid="{0C40B920-85AA-4EBD-942C-6D362E066F93}"/>
+    <hyperlink ref="E5" r:id="rId53" xr:uid="{FB43C47B-080B-425D-AE49-7CB66FFCA877}"/>
+    <hyperlink ref="E20" r:id="rId54" xr:uid="{ADA410F7-2033-42E9-893C-C73BEC52BBB3}"/>
+    <hyperlink ref="E86" r:id="rId55" xr:uid="{C68CE6CF-B1D8-4496-8ACA-B22291EF52D0}"/>
+    <hyperlink ref="E19" r:id="rId56" xr:uid="{689C7FE7-936A-4F5D-8BE8-0E06ACB96066}"/>
+    <hyperlink ref="E4" r:id="rId57" xr:uid="{56931A3E-09F5-4F5F-94F1-E75BB9C6DFC6}"/>
+    <hyperlink ref="E57" r:id="rId58" xr:uid="{2E6A6A58-722B-4B19-B4B8-9398626D7004}"/>
+    <hyperlink ref="E67" r:id="rId59" display="https://doi.org/10.1088/1742-6596/1986/1/012102?urlappend=%3Futm_source%3Dresearchgate.net%26medium%3Darticle" xr:uid="{E41E8DBF-54EA-4416-A23A-A0A78B3D3697}"/>
+    <hyperlink ref="E30" r:id="rId60" xr:uid="{1E5241C9-DBD6-4C59-AFAC-6620AE75E3AE}"/>
+    <hyperlink ref="E29" r:id="rId61" xr:uid="{297F2160-7FDA-4E61-8889-0B71276CD383}"/>
+    <hyperlink ref="E51" r:id="rId62" xr:uid="{72EECF10-CECD-464C-BB04-C3AB1A2473B5}"/>
+    <hyperlink ref="E71" r:id="rId63" xr:uid="{DCECEEEA-CC5C-4A5C-997B-17BED3201EE9}"/>
+    <hyperlink ref="E6" r:id="rId64" xr:uid="{00A5E618-BEB1-45F3-A05E-F2CC3A86EBE1}"/>
+    <hyperlink ref="E75" r:id="rId65" xr:uid="{FE8EA63D-DF79-4D3A-A081-43562A92D5E5}"/>
+    <hyperlink ref="E56" r:id="rId66" xr:uid="{E6C3BB6B-F8FC-42D8-8A3B-069A6360CF02}"/>
+    <hyperlink ref="E78" r:id="rId67" xr:uid="{6182ED48-FC33-4E17-89BD-BF1C73B01713}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" r:id="rId68"/>
